--- a/data/ams_weekly_data/Nexlev/ads_report_week15.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week15.xlsx
@@ -7651,7 +7651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7747,19 +7747,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1490</v>
+        <v>701</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>227.08</v>
+        <v>106.9069402118998</v>
       </c>
       <c r="G3" t="n">
-        <v>7194.91</v>
+        <v>3387.29</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -7771,28 +7771,28 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_GS-05_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HPC_SBV_KT_LE-02_B0DCGHKRXX_Reel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3332</v>
+        <v>789</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>1444.51</v>
+        <v>120.1730597881002</v>
       </c>
       <c r="G4" t="n">
-        <v>1566.94</v>
+        <v>3807.62</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7804,28 +7804,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SBV_KT_GS-05_BCG_Phrase &amp; Exact_Reel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>3332</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>22.33</v>
+        <v>1444.51</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1566.94</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_BCG_Phrase &amp; Exact_Reel_CPM</t>
+          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_BCG_Phrase &amp; Exact_Reel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7846,13 +7846,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2.89</v>
+        <v>22.33</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_BCG_Phrase &amp; Exact_Reel_CPM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7879,13 +7879,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2003</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1671.89</v>
+        <v>2.89</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -7903,28 +7903,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nex_HnK_SBV_KT_SC-05_B0F43P6D23_BCG_Phrase &amp; Exact_Reel</t>
+          <t>Nex_HnK_SBV_KT_MR-01_B0CYSLCRQS_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5804</v>
+        <v>2003</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>2821.353333333333</v>
+        <v>1671.89</v>
       </c>
       <c r="G8" t="n">
-        <v>6322.316666666667</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7941,23 +7941,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5804</v>
+        <v>7825</v>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="F9" t="n">
-        <v>2821.353333333333</v>
+        <v>3803.60050733662</v>
       </c>
       <c r="G9" t="n">
-        <v>6322.316666666667</v>
+        <v>8523.415552657745</v>
       </c>
       <c r="H9" t="n">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7978,19 +7978,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5804</v>
+        <v>9587</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>213</v>
       </c>
       <c r="F10" t="n">
-        <v>2821.353333333333</v>
+        <v>4660.459492663379</v>
       </c>
       <c r="G10" t="n">
-        <v>6322.316666666667</v>
+        <v>10443.53444734226</v>
       </c>
       <c r="H10" t="n">
-        <v>2.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8011,19 +8011,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18728.33333333333</v>
+        <v>39673</v>
       </c>
       <c r="E11" t="n">
-        <v>32.66666666666666</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>431.98</v>
+        <v>915.0734868141863</v>
       </c>
       <c r="G11" t="n">
-        <v>20280.80666666667</v>
+        <v>42961.3141160958</v>
       </c>
       <c r="H11" t="n">
-        <v>7.333333333333333</v>
+        <v>28</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8044,19 +8044,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18728.33333333333</v>
+        <v>16512</v>
       </c>
       <c r="E12" t="n">
-        <v>32.66666666666666</v>
+        <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>431.98</v>
+        <v>380.8665131858139</v>
       </c>
       <c r="G12" t="n">
-        <v>20280.80666666667</v>
+        <v>17881.10588390422</v>
       </c>
       <c r="H12" t="n">
-        <v>7.333333333333333</v>
+        <v>12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8068,28 +8068,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_GS-02/05_B0CDPMX152_B0D383WQPB</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18728.33333333333</v>
+        <v>55122</v>
       </c>
       <c r="E13" t="n">
-        <v>32.66666666666666</v>
+        <v>651</v>
       </c>
       <c r="F13" t="n">
-        <v>431.98</v>
+        <v>13017.19113689453</v>
       </c>
       <c r="G13" t="n">
-        <v>20280.80666666667</v>
+        <v>32098.19616048875</v>
       </c>
       <c r="H13" t="n">
-        <v>7.333333333333333</v>
+        <v>11</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8106,23 +8106,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26253</v>
+        <v>5212</v>
       </c>
       <c r="E14" t="n">
-        <v>313</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>6254.566666666667</v>
+        <v>1220.828455156427</v>
       </c>
       <c r="G14" t="n">
-        <v>15235.59666666667</v>
+        <v>3044.13491841736</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8143,19 +8143,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26253</v>
+        <v>9366</v>
       </c>
       <c r="E15" t="n">
-        <v>313</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>6254.566666666667</v>
+        <v>2298.757144874649</v>
       </c>
       <c r="G15" t="n">
-        <v>15235.59666666667</v>
+        <v>5371.788328129866</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8176,19 +8176,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26253</v>
+        <v>9059</v>
       </c>
       <c r="E16" t="n">
-        <v>313</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
-        <v>6254.566666666667</v>
+        <v>2226.92326307439</v>
       </c>
       <c r="G16" t="n">
-        <v>15235.59666666667</v>
+        <v>5192.670592964025</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8209,19 +8209,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4233.5</v>
+        <v>2313</v>
       </c>
       <c r="E17" t="n">
-        <v>144.5</v>
+        <v>79</v>
       </c>
       <c r="F17" t="n">
-        <v>2168.625</v>
+        <v>1184.759089469833</v>
       </c>
       <c r="G17" t="n">
-        <v>9758.82</v>
+        <v>5331.420000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8238,23 +8238,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4233.5</v>
+        <v>2479</v>
       </c>
       <c r="E18" t="n">
-        <v>144.5</v>
+        <v>85</v>
       </c>
       <c r="F18" t="n">
-        <v>2168.625</v>
+        <v>1269.63013535448</v>
       </c>
       <c r="G18" t="n">
-        <v>9758.82</v>
+        <v>5713.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8266,28 +8266,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4628.5</v>
+        <v>3676</v>
       </c>
       <c r="E19" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="F19" t="n">
-        <v>774.28</v>
+        <v>1882.860775175687</v>
       </c>
       <c r="G19" t="n">
-        <v>2795.34</v>
+        <v>8472.879999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8304,23 +8304,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4628.5</v>
+        <v>9257</v>
       </c>
       <c r="E20" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="F20" t="n">
-        <v>774.28</v>
+        <v>1548.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2795.34</v>
+        <v>5590.68</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -8341,16 +8341,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42340</v>
+        <v>42124</v>
       </c>
       <c r="E21" t="n">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="F21" t="n">
-        <v>14284.76</v>
+        <v>14211.7378034159</v>
       </c>
       <c r="G21" t="n">
-        <v>53641.55</v>
+        <v>53367.15695630291</v>
       </c>
       <c r="H21" t="n">
         <v>18</v>
@@ -8365,28 +8365,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1659.5</v>
+        <v>216</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>490.77</v>
+        <v>73.02219658410253</v>
       </c>
       <c r="G22" t="n">
-        <v>1903.81</v>
+        <v>274.3930436970869</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8407,19 +8407,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1659.5</v>
+        <v>3319</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="F23" t="n">
-        <v>490.77</v>
+        <v>981.54</v>
       </c>
       <c r="G23" t="n">
-        <v>1903.81</v>
+        <v>3807.62</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8436,23 +8436,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16173</v>
+        <v>4800</v>
       </c>
       <c r="E24" t="n">
-        <v>758</v>
+        <v>225</v>
       </c>
       <c r="F24" t="n">
-        <v>11719.98</v>
+        <v>3478.407427782271</v>
       </c>
       <c r="G24" t="n">
-        <v>27807.36</v>
+        <v>8253.028381534406</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -8464,28 +8464,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>962.3333333333334</v>
+        <v>2501</v>
       </c>
       <c r="E25" t="n">
-        <v>10.33333333333333</v>
+        <v>117</v>
       </c>
       <c r="F25" t="n">
-        <v>249.6966666666667</v>
+        <v>1812.706832317505</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4300.911047690567</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -8497,25 +8497,25 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>962.3333333333334</v>
+        <v>759</v>
       </c>
       <c r="E26" t="n">
-        <v>10.33333333333333</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>249.6966666666667</v>
+        <v>550.1775781952709</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1305.376458048909</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -8530,28 +8530,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>962.3333333333334</v>
+        <v>8112</v>
       </c>
       <c r="E27" t="n">
-        <v>10.33333333333333</v>
+        <v>380</v>
       </c>
       <c r="F27" t="n">
-        <v>249.6966666666667</v>
+        <v>5878.688161704954</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>13948.04411272612</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -8563,22 +8563,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29268.5</v>
+        <v>962</v>
       </c>
       <c r="E28" t="n">
-        <v>35.5</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>409.705</v>
+        <v>249.6966666666667</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -8596,30 +8596,129 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>962</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>249.6966666666667</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>962</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>249.6966666666667</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>29268</v>
+      </c>
+      <c r="E31" t="n">
+        <v>36</v>
+      </c>
+      <c r="F31" t="n">
+        <v>409.705</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>B0DCK7ZH5P</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>29268.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="D32" t="n">
+        <v>29268</v>
+      </c>
+      <c r="E32" t="n">
+        <v>36</v>
+      </c>
+      <c r="F32" t="n">
         <v>409.705</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week15.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week15.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
